--- a/public/synonyms.xlsx
+++ b/public/synonyms.xlsx
@@ -1,58 +1,828 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="26860" windowHeight="11940"/>
+  </bookViews>
   <sheets>
     <sheet name="同义词映射" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="128">
+  <si>
+    <t>term1</t>
+  </si>
+  <si>
+    <t>term2</t>
+  </si>
+  <si>
+    <t>百万元港币</t>
+  </si>
+  <si>
+    <t>百萬港元</t>
+  </si>
+  <si>
+    <t>立方米</t>
+  </si>
+  <si>
+    <t>m³</t>
+  </si>
+  <si>
+    <t>千克</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>吨</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>人民币</t>
+  </si>
+  <si>
+    <t>RMB</t>
+  </si>
+  <si>
+    <t>美元</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>兆瓦时</t>
+  </si>
+  <si>
+    <t>MWh</t>
+  </si>
+  <si>
+    <t>tCO2e</t>
+  </si>
+  <si>
+    <t>吨二氧化碳当量</t>
+  </si>
+  <si>
+    <t>千瓦时</t>
+  </si>
+  <si>
+    <t>亿度</t>
+  </si>
+  <si>
+    <t>kgCO2e</t>
+  </si>
+  <si>
+    <t>公斤二氧化碳當量</t>
+  </si>
+  <si>
+    <t>吨CO2e</t>
+  </si>
+  <si>
+    <t>公噸</t>
+  </si>
+  <si>
+    <t>百万元营收</t>
+  </si>
+  <si>
+    <t>百萬人民幣收入</t>
+  </si>
+  <si>
+    <t>万元营收</t>
+  </si>
+  <si>
+    <t>万元人民币</t>
+  </si>
+  <si>
+    <t>吉焦</t>
+  </si>
+  <si>
+    <t>千兆焦耳(GJ)</t>
+  </si>
+  <si>
+    <t>损失工作日</t>
+  </si>
+  <si>
+    <t>损失天数</t>
+  </si>
+  <si>
+    <t>事故件数</t>
+  </si>
+  <si>
+    <t>件</t>
+  </si>
+  <si>
+    <t>二氧化碳當量(噸)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>噸CO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>₂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>當量</t>
+    </r>
+  </si>
+  <si>
+    <t>公斤标煤</t>
+  </si>
+  <si>
+    <t>千克标煤</t>
+  </si>
+  <si>
+    <t>立方米/百万元港币</t>
+  </si>
+  <si>
+    <t>立方米/百萬港元</t>
+  </si>
+  <si>
+    <t>吨/百万元港币</t>
+  </si>
+  <si>
+    <t>公噸/百萬港元</t>
+  </si>
+  <si>
+    <t>兆瓦时/百万元港币</t>
+  </si>
+  <si>
+    <t>兆瓦時/百萬港元</t>
+  </si>
+  <si>
+    <t>tCO2e/百万元港币</t>
+  </si>
+  <si>
+    <t>公噸二氧化碳當量/百萬港元</t>
+  </si>
+  <si>
+    <t>兆瓦時</t>
+  </si>
+  <si>
+    <t>公噸二氧化碳當量</t>
+  </si>
+  <si>
+    <t>小时</t>
+  </si>
+  <si>
+    <t>小時</t>
+  </si>
+  <si>
+    <t>万</t>
+  </si>
+  <si>
+    <t>万元</t>
+  </si>
+  <si>
+    <t>起</t>
+  </si>
+  <si>
+    <t>次</t>
+  </si>
+  <si>
+    <t>tCO₂e</t>
+  </si>
+  <si>
+    <t>亿</t>
+  </si>
+  <si>
+    <t>亿元</t>
+  </si>
+  <si>
+    <t>千瓦時</t>
+  </si>
+  <si>
+    <t>噸</t>
+  </si>
+  <si>
+    <t>吨/百万元营收</t>
+  </si>
+  <si>
+    <t>噸/百萬人民幣收入</t>
+  </si>
+  <si>
+    <t>tCO2e/百万元营收</t>
+  </si>
+  <si>
+    <t>吨二氧化碳当量/百万元</t>
+  </si>
+  <si>
+    <t>千克/万元营收</t>
+  </si>
+  <si>
+    <t>kg/万元人民币</t>
+  </si>
+  <si>
+    <t>吉焦/百万元营收</t>
+  </si>
+  <si>
+    <t>千兆焦耳(GJ)/百万人民币</t>
+  </si>
+  <si>
+    <t>tCO2e/万元营收</t>
+  </si>
+  <si>
+    <t>吨CO2e/万元CNY</t>
+  </si>
+  <si>
+    <t>吨/万元营收</t>
+  </si>
+  <si>
+    <t>吨/万元人民币</t>
+  </si>
+  <si>
+    <t>GJ/百万CNY</t>
+  </si>
+  <si>
+    <t>千度(MWh)</t>
+  </si>
+  <si>
+    <t>升</t>
+  </si>
+  <si>
+    <t>公升(L)</t>
+  </si>
+  <si>
+    <t>立方公尺(m³)</t>
+  </si>
+  <si>
+    <t>公吨</t>
+  </si>
+  <si>
+    <t>噸二氧化碳當量</t>
+  </si>
+  <si>
+    <t>萬元</t>
+  </si>
+  <si>
+    <t>吨CO₂e</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>比例</t>
+  </si>
+  <si>
+    <t>億</t>
+  </si>
+  <si>
+    <t>噸/百萬元營業收入</t>
+  </si>
+  <si>
+    <t>例</t>
+  </si>
+  <si>
+    <t>tCO₂e/百万人民币</t>
+  </si>
+  <si>
+    <t>百万</t>
+  </si>
+  <si>
+    <t>百万元</t>
+  </si>
+  <si>
+    <t>二氧化碳當量(噸)/萬元人民幣</t>
+  </si>
+  <si>
+    <t>事故件数/百万工时</t>
+  </si>
+  <si>
+    <t>次/百萬工時</t>
+  </si>
+  <si>
+    <t>百萬元</t>
+  </si>
+  <si>
+    <t>tonnes CO₂e/million RMB</t>
+  </si>
+  <si>
+    <t>tonnes</t>
+  </si>
+  <si>
+    <t>tonnes CO₂e</t>
+  </si>
+  <si>
+    <t>千吨</t>
+  </si>
+  <si>
+    <t>千噸</t>
+  </si>
+  <si>
+    <t>百萬立方米</t>
+  </si>
+  <si>
+    <t>噸CO2-當量</t>
+  </si>
+  <si>
+    <t>吉焦耳</t>
+  </si>
+  <si>
+    <t>人</t>
+  </si>
+  <si>
+    <t>名員工</t>
+  </si>
+  <si>
+    <t>宗</t>
+  </si>
+  <si>
+    <t>千克/单位产品</t>
+  </si>
+  <si>
+    <t>千克/每貨運單位</t>
+  </si>
+  <si>
+    <t>公斤/每出貨單位</t>
+  </si>
+  <si>
+    <t>公斤</t>
+  </si>
+  <si>
+    <t>天</t>
+  </si>
+  <si>
+    <t>個工作日數</t>
+  </si>
+  <si>
+    <t>日數</t>
+  </si>
+  <si>
+    <t>時數</t>
+  </si>
+  <si>
+    <t>吨/辆</t>
+  </si>
+  <si>
+    <t>噸/輛</t>
+  </si>
+  <si>
+    <t>千克/辆</t>
+  </si>
+  <si>
+    <t>千克/輛</t>
+  </si>
+  <si>
+    <t>公斤标煤/辆</t>
+  </si>
+  <si>
+    <t>千克標準煤/輛</t>
+  </si>
+  <si>
+    <t>tCO2e/辆</t>
+  </si>
+  <si>
+    <t>噸二氧化碳當量/輛</t>
+  </si>
+  <si>
+    <t>事故件数/二十万工时</t>
+  </si>
+  <si>
+    <t>n/20萬工作小時</t>
+  </si>
+  <si>
+    <t>吨/人</t>
+  </si>
+  <si>
+    <t>噸/人</t>
+  </si>
+  <si>
+    <t>tCO2e/人</t>
+  </si>
+  <si>
+    <t>吨二氧化碳当量/人</t>
+  </si>
+  <si>
+    <t>吨二氧化碳当量/万元营收</t>
+  </si>
+  <si>
+    <t>吨标煤</t>
+  </si>
+  <si>
+    <t>吨标准煤</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="24">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -60,18 +830,316 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -209,7 +1277,6 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
@@ -220,27 +1287,31 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
+              <a:shade val="9500"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -262,7 +1333,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -320,7 +1391,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:tint val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -333,13 +1404,12 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
+                <a:tint val="80000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -351,113 +1421,743 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:B90"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="2" width="13.0096153846154" style="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>term1</v>
-      </c>
-      <c r="B1" t="str">
-        <v>term2</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>百万元港币</v>
-      </c>
-      <c r="B2" t="str">
-        <v>百萬港元</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>立方米</v>
-      </c>
-      <c r="B3" t="str">
-        <v>m³</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>千克</v>
-      </c>
-      <c r="B4" t="str">
-        <v>kg</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>吨</v>
-      </c>
-      <c r="B5" t="str">
-        <v>t</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>人民币</v>
-      </c>
-      <c r="B6" t="str">
-        <v>RMB</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>美元</v>
-      </c>
-      <c r="B7" t="str">
-        <v>USD</v>
+    <row r="1" ht="18" customHeight="1" spans="1:2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" ht="19.5" customHeight="1" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" ht="19.5" customHeight="1" spans="1:2">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" ht="19.5" customHeight="1" spans="1:2">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" ht="19.5" customHeight="1" spans="1:2">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" ht="19.5" customHeight="1" spans="1:2">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" ht="19.5" customHeight="1" spans="1:2">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" ht="19.5" customHeight="1" spans="1:2">
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" ht="17.6" spans="1:2">
+      <c r="A9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" ht="17.6" spans="1:2">
+      <c r="A10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" ht="17.6" spans="1:2">
+      <c r="A11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" ht="17.6" spans="1:2">
+      <c r="A12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" ht="17.6" spans="1:2">
+      <c r="A13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" ht="17.6" spans="1:2">
+      <c r="A14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" ht="17.6" spans="1:2">
+      <c r="A15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" ht="17.6" spans="1:2">
+      <c r="A16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" ht="17.6" spans="1:2">
+      <c r="A17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" ht="17.6" spans="1:2">
+      <c r="A18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" ht="17.6" spans="1:2">
+      <c r="A19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" ht="18" spans="1:2">
+      <c r="A20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" ht="17.6" spans="1:2">
+      <c r="A21" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" ht="17.6" spans="1:2">
+      <c r="A22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" ht="17.6" spans="1:2">
+      <c r="A23" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" ht="17.6" spans="1:2">
+      <c r="A24" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" ht="17.6" spans="1:2">
+      <c r="A25" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" ht="17.6" spans="1:2">
+      <c r="A26" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" ht="17.6" spans="1:2">
+      <c r="A27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" ht="17.6" spans="1:2">
+      <c r="A28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" ht="17.6" spans="1:2">
+      <c r="A29" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" ht="17.6" spans="1:2">
+      <c r="A30" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" ht="17.6" spans="1:2">
+      <c r="A31" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" ht="17.6" spans="1:2">
+      <c r="A32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" ht="17.6" spans="1:2">
+      <c r="A33" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" ht="17.6" spans="1:2">
+      <c r="A34" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" ht="17.6" spans="1:2">
+      <c r="A35" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" ht="17.6" spans="1:2">
+      <c r="A36" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" ht="17.6" spans="1:2">
+      <c r="A37" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" ht="17.6" spans="1:2">
+      <c r="A38" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" ht="17.6" spans="1:2">
+      <c r="A39" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" ht="17.6" spans="1:2">
+      <c r="A40" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="41" ht="17.6" spans="1:2">
+      <c r="A41" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" ht="17.6" spans="1:2">
+      <c r="A42" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" ht="17.6" spans="1:2">
+      <c r="A43" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" ht="17.6" spans="1:2">
+      <c r="A44" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" ht="17.6" spans="1:2">
+      <c r="A45" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" ht="17.6" spans="1:2">
+      <c r="A46" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="47" ht="17.6" spans="1:2">
+      <c r="A47" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="48" ht="17.6" spans="1:2">
+      <c r="A48" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="49" ht="17.6" spans="1:2">
+      <c r="A49" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50" ht="17.6" spans="1:2">
+      <c r="A50" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" ht="17.6" spans="1:2">
+      <c r="A51" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="52" ht="17.6" spans="1:2">
+      <c r="A52" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" ht="17.6" spans="1:2">
+      <c r="A53" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="54" ht="17.6" spans="1:2">
+      <c r="A54" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="55" ht="17.6" spans="1:2">
+      <c r="A55" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="56" ht="17.6" spans="1:2">
+      <c r="A56" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="57" ht="17.6" spans="1:2">
+      <c r="A57" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="58" ht="17.6" spans="1:2">
+      <c r="A58" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" ht="17.6" spans="1:2">
+      <c r="A59" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="60" ht="17.6" spans="1:2">
+      <c r="A60" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="61" ht="17.6" spans="1:2">
+      <c r="A61" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="62" ht="17.6" spans="1:2">
+      <c r="A62" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="63" ht="17.6" spans="1:2">
+      <c r="A63" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="64" ht="17.6" spans="1:2">
+      <c r="A64" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="65" ht="17.6" spans="1:2">
+      <c r="A65" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" ht="17.6" spans="1:2">
+      <c r="A66" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" ht="17.6" spans="1:2">
+      <c r="A67" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="68" ht="17.6" spans="1:2">
+      <c r="A68" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" ht="17.6" spans="1:2">
+      <c r="A69" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="70" ht="17.6" spans="1:2">
+      <c r="A70" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="71" ht="17.6" spans="1:2">
+      <c r="A71" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="72" ht="17.6" spans="1:2">
+      <c r="A72" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="73" ht="17.6" spans="1:2">
+      <c r="A73" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="74" ht="17.6" spans="1:2">
+      <c r="A74" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="75" ht="17.6" spans="1:2">
+      <c r="A75" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="76" ht="17.6" spans="1:2">
+      <c r="A76" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="77" ht="17.6" spans="1:2">
+      <c r="A77" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="78" ht="17.6" spans="1:2">
+      <c r="A78" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="79" ht="17.6" spans="1:2">
+      <c r="A79" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="80" ht="17.6" spans="1:2">
+      <c r="A80" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="81" ht="17.6" spans="1:2">
+      <c r="A81" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="82" ht="17.6" spans="1:2">
+      <c r="A82" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="83" ht="17.6" spans="1:2">
+      <c r="A83" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="84" ht="17.6" spans="1:2">
+      <c r="A84" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="85" ht="17.6" spans="1:2">
+      <c r="A85" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="86" ht="17.6" spans="1:2">
+      <c r="A86" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="87" ht="17.6" spans="1:2">
+      <c r="A87" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="88" ht="17.6" spans="1:2">
+      <c r="A88" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="89" ht="17.6" spans="1:2">
+      <c r="A89" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="90" ht="17.6" spans="1:2">
+      <c r="A90" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/public/synonyms.xlsx
+++ b/public/synonyms.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26860" windowHeight="11940"/>
+    <workbookView windowWidth="21140" windowHeight="11940"/>
   </bookViews>
   <sheets>
     <sheet name="同义词映射" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="151">
   <si>
     <t>term1</t>
   </si>
@@ -438,6 +438,99 @@
   <si>
     <t>吨标准煤</t>
   </si>
+  <si>
+    <t>万元CNY</t>
+  </si>
+  <si>
+    <t>吨钢</t>
+  </si>
+  <si>
+    <t>吨产品</t>
+  </si>
+  <si>
+    <t>吨粗钢</t>
+  </si>
+  <si>
+    <t>百万CNY</t>
+  </si>
+  <si>
+    <t>百万工时</t>
+  </si>
+  <si>
+    <t>千兆焦耳（GJ）</t>
+  </si>
+  <si>
+    <t>吨碳</t>
+  </si>
+  <si>
+    <t>人数</t>
+  </si>
+  <si>
+    <t>人次</t>
+  </si>
+  <si>
+    <t>克/吨产品</t>
+  </si>
+  <si>
+    <t>克/吨</t>
+  </si>
+  <si>
+    <t>千克/吨产品</t>
+  </si>
+  <si>
+    <t>千克/吨</t>
+  </si>
+  <si>
+    <t>吉焦/吨产品</t>
+  </si>
+  <si>
+    <t>吉焦/吨粗钢</t>
+  </si>
+  <si>
+    <t>千兆焦耳（GJ）/百万CNY</t>
+  </si>
+  <si>
+    <t>吨/万元</t>
+  </si>
+  <si>
+    <t>吨/吨产品</t>
+  </si>
+  <si>
+    <t>吨碳/吨钢</t>
+  </si>
+  <si>
+    <t>立方公尺(m3)</t>
+  </si>
+  <si>
+    <r>
+      <t>吨/万元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.25"/>
+        <color rgb="FF0F172A"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>营收</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>吨/万元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.25"/>
+        <color rgb="FF0F172A"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>产值</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -449,7 +542,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -471,8 +564,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="8.25"/>
+      <color rgb="FF166534"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -622,6 +716,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8.25"/>
+      <color rgb="FF0F172A"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -931,19 +1032,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -952,7 +1053,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1076,12 +1177,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1430,7 +1533,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:B90"/>
+  <dimension ref="A1:B126"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="2" width="13.0096153846154" style="1" customWidth="1"/>
@@ -2156,6 +2259,294 @@
         <v>127</v>
       </c>
     </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
